--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:45</t>
+    <t xml:space="preserve">2026-09-09 23:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:45</t>
+    <t xml:space="preserve">2026-09-18 10:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:34</t>
+    <t xml:space="preserve">2026-09-23 13:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 13:06</t>
+    <t xml:space="preserve">2026-10-02 15:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_nuble.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">San Nicolás</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">San Ignacio</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:27</t>
+    <t xml:space="preserve">2026-10-04 09:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:52</t>
+    <t xml:space="preserve">2026-10-05 13:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -714,7 +714,7 @@
         <v>2019</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>77266.62</v>
+        <v>77266.63</v>
       </c>
     </row>
     <row r="13">
@@ -850,7 +850,7 @@
         <v>2019</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>73038.12</v>
+        <v>73038.13</v>
       </c>
     </row>
     <row r="21">
